--- a/04_DESIGN_TABLES/DesignTable_2706.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2706.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1615,12 +1620,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>Air-Way s74 only (double-pass 25 rows)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L25@DRIVE=2.92~2.920; C2HEX@HEX=1.38~1.375; D1@BORE=0.72~0.719; D@BORE=0.61~0.609</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1678,12 +1688,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>Air-Way s74 only (double-pass 25 rows)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L25@DRIVE=2.92~2.920; C2HEX@HEX=1.38~1.375; D1@BORE=0.72~0.719; D@BORE=0.61~0.609</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2086,24 +2101,55 @@
           <t>2706-04-02</t>
         </is>
       </c>
+      <c r="B28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1/8</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>2706-04-02</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1/4-18 (A NPTF) x 5/16-24 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1070 "Overall Length" = 1.980 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "L LGTH" = "1.980" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; C2HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1070 "Hex Flat" = 0.625 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "C1 HEX" = "0.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1070 "Side 1 ID" = 0.281 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "A1 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1070 "Side 2 ID" = 0.062 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "B2 DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; I1@DRIVE: own Brennan STEP 09_STEP_FILES/BRENNAN_2706-04-02.stp (sha256 d4ff2da4fb37563b...) measured with wave2/straight/scripts/measure_bulkhead.py (validated on Brennan 2705-08-08 = Air-Way I1 1.44): bulkhead tip 1.42 - relief start 0.31 = 1.11; STEP overall 1.98 = OMi / catalog 1.980, hex 0.6251 = 0.625 [Brennan = yes 2026-10-18]; THDMAJ_A@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD; OMi Items!U1070 "1/4-18 NPTF"; THDMAJ_B@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; OMi Items!AA1070 "5/16-24 UNF"; $PRP@TubeOD: Brennan TFA p9 TFA-p009-t01 row 2706-04-02 col "TUBE O.D." = "1/8" (= the -02 JIC tube; format of the built 2706 rows); $PRP@Threads: thread texts from the part-number dashes (NPTF[4] / JIC[2]), format of the built 2706 rows</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L25 / hex / bores from OMi Items (= Brennan TFA p9); I1 measured on the Brennan 2706-04-02 STEP (no Air-Way -02 bulkhead)</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2114,6 +2160,11 @@
       <c r="P28" t="inlineStr">
         <is>
           <t>2706-04-02</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2197,24 +2248,55 @@
           <t>2706-LN-04-02</t>
         </is>
       </c>
+      <c r="B31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1/8</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>2706-LN-04-02</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1/4-18 (A NPTF) x 5/16-24 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1085 "Overall Length" = 1.980 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "L LGTH" = "1.980" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; C2HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1085 "Hex Flat" = 0.625 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "C1 HEX" = "0.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1085 "Side 1 ID" = 0.281 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "A1 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1085 "Side 2 ID" = 0.062 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "B2 DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; I1@DRIVE: own Brennan STEP 09_STEP_FILES/BRENNAN_2706-04-02.stp (sha256 d4ff2da4fb37563b...) measured with wave2/straight/scripts/measure_bulkhead.py (validated on Brennan 2705-08-08 = Air-Way I1 1.44): bulkhead tip 1.42 - relief start 0.31 = 1.11; STEP overall 1.98 = OMi / catalog 1.980, hex 0.6251 = 0.625 [Brennan = yes 2026-10-18] [the -LN part = the plain 2706-04-02 + a locknut: Q-TRANSFER-LN open]; THDMAJ_A@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD; OMi Items!U1085 "1/4-18 NPTF"; THDMAJ_B@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; OMi Items!AA1085 "5/16-24 UNF"; $PRP@TubeOD: Brennan TFA p9 TFA-p009-t01 row 2706-04-02 col "TUBE O.D." = "1/8" (= the -02 JIC tube; format of the built 2706 rows); $PRP@Threads: thread texts from the part-number dashes (NPTF[4] / JIC[2]), format of the built 2706 rows</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L25 / hex / bores from OMi Items (= Brennan TFA p9); I1 measured on the Brennan 2706-04-02 STEP (no Air-Way -02 bulkhead) - copied from the plain part (Q-TRANSFER-LN)</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2225,6 +2307,11 @@
       <c r="P31" t="inlineStr">
         <is>
           <t>2706-LN-04-02</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_2706.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2706.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,7 +521,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.172</v>
+        <v>0.19</v>
       </c>
       <c r="F3" t="n">
         <v>0.17</v>
@@ -554,7 +554,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1069 Side 1 ID = 0.172 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1069 Side 1 ID = 0.172 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: Air-Way 0.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.172) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.172 -&gt; Air-Way 0.19</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -584,7 +589,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.172</v>
+        <v>0.19</v>
       </c>
       <c r="F4" t="n">
         <v>0.17</v>
@@ -617,7 +622,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1084 Side 1 ID = 0.172 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1084 Side 1 ID = 0.172 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: Air-Way 0.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.172) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.172 -&gt; Air-Way 0.19</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -638,7 +648,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="C5" t="n">
         <v>1.2</v>
@@ -680,7 +690,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1071 Overall Length = 2.080 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1071 Overall Length = 2.080 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.03 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.08) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.08 -&gt; Air-Way 2.03</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -701,7 +716,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="C6" t="n">
         <v>1.2</v>
@@ -743,7 +758,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1086 Overall Length = 2.080 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1086 Overall Length = 2.080 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.03 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.08) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.08 -&gt; Air-Way 2.03</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -764,7 +784,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="C7" t="n">
         <v>1.28</v>
@@ -776,7 +796,7 @@
         <v>0.28</v>
       </c>
       <c r="F7" t="n">
-        <v>0.281</v>
+        <v>0.3</v>
       </c>
       <c r="G7" t="n">
         <v>0.54</v>
@@ -806,7 +826,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1072 Overall Length = 2.180 (table had 2.19); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1072 Side 2 ID = 0.281 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1072 Overall Length = 2.180 (table had 2.19); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1072 Side 2 ID = 0.281 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D@BORE: Air-Way 0.3 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.281) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.18 -&gt; Air-Way 2.19 | 2026-10-20 Air-Way first: D@BORE OMi/Brennan 0.281 -&gt; Air-Way 0.3</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -827,7 +852,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="C8" t="n">
         <v>1.28</v>
@@ -839,7 +864,7 @@
         <v>0.28</v>
       </c>
       <c r="F8" t="n">
-        <v>0.281</v>
+        <v>0.3</v>
       </c>
       <c r="G8" t="n">
         <v>0.54</v>
@@ -869,7 +894,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1087 Overall Length = 2.180 (table had 2.19); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1087 Side 2 ID = 0.281 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1087 Overall Length = 2.180 (table had 2.19); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1087 Side 2 ID = 0.281 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D@BORE: Air-Way 0.3 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.281) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.18 -&gt; Air-Way 2.19 | 2026-10-20 Air-Way first: D@BORE OMi/Brennan 0.281 -&gt; Air-Way 0.3</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -890,7 +920,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="C9" t="n">
         <v>1.28</v>
@@ -932,7 +962,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1074 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1074 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.18 -&gt; Air-Way 2.19</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -953,7 +988,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="C10" t="n">
         <v>1.28</v>
@@ -995,7 +1030,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1089 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1089 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.18 -&gt; Air-Way 2.19</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1016,7 +1056,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="C11" t="n">
         <v>1.44</v>
@@ -1025,7 +1065,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.391</v>
+        <v>0.41</v>
       </c>
       <c r="F11" t="n">
         <v>0.39</v>
@@ -1058,7 +1098,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1075 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1075 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1075 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1075 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.36 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.35) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.41 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.391) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.35 -&gt; Air-Way 2.36 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.391 -&gt; Air-Way 0.41</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1079,7 +1124,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="C12" t="n">
         <v>1.44</v>
@@ -1088,7 +1133,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.391</v>
+        <v>0.41</v>
       </c>
       <c r="F12" t="n">
         <v>0.39</v>
@@ -1121,7 +1166,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1090 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1090 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1090 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1090 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.36 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.35) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.41 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.391) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.35 -&gt; Air-Way 2.36 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.391 -&gt; Air-Way 0.41</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1142,7 +1192,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="C13" t="n">
         <v>1.28</v>
@@ -1184,7 +1234,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1076 Overall Length = 2.400 (table had 2.34) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1076 Overall Length = 2.400 (table had 2.34) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.4) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.4 -&gt; Air-Way 2.34</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1205,7 +1260,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="C14" t="n">
         <v>1.44</v>
@@ -1247,7 +1302,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1077 Overall Length = 2.600 (table had 2.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1077 Overall Length = 2.600 (table had 2.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.6) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.6 -&gt; Air-Way 2.53</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1268,7 +1328,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="C15" t="n">
         <v>1.44</v>
@@ -1310,7 +1370,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1092 Overall Length = 2.600 (table had 2.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1092 Overall Length = 2.600 (table had 2.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.6) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.6 -&gt; Air-Way 2.53</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1331,7 +1396,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="C16" t="n">
         <v>1.58</v>
@@ -1340,7 +1405,7 @@
         <v>1.13</v>
       </c>
       <c r="E16" t="n">
-        <v>0.484</v>
+        <v>0.53</v>
       </c>
       <c r="F16" t="n">
         <v>0.48</v>
@@ -1373,7 +1438,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1078 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1078 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1078 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1078 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.8) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.484) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.8 -&gt; Air-Way 2.72 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.484 -&gt; Air-Way 0.53</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1394,7 +1464,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="C17" t="n">
         <v>1.58</v>
@@ -1403,7 +1473,7 @@
         <v>1.13</v>
       </c>
       <c r="E17" t="n">
-        <v>0.484</v>
+        <v>0.53</v>
       </c>
       <c r="F17" t="n">
         <v>0.48</v>
@@ -1436,7 +1506,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1093 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1093 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1093 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1093 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.8) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.484) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.8 -&gt; Air-Way 2.72 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.484 -&gt; Air-Way 0.53</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1719,7 +1794,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="C22" t="n">
         <v>1.75</v>
@@ -1761,7 +1836,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1080 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1080 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.17 -&gt; Air-Way 3.11</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1782,7 +1862,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="C23" t="n">
         <v>1.75</v>
@@ -1824,7 +1904,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1095 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1095 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.17 -&gt; Air-Way 3.11</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1845,7 +1930,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="C24" t="n">
         <v>1.8</v>
@@ -1887,7 +1972,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1081 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1081 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.32) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.32 -&gt; Air-Way 3.25</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -1908,7 +1998,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="C25" t="n">
         <v>1.8</v>
@@ -1950,7 +2040,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1096 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1096 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.32) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.32 -&gt; Air-Way 3.25</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -1971,7 +2066,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="C26" t="n">
         <v>1.81</v>
@@ -1980,7 +2075,7 @@
         <v>2.13</v>
       </c>
       <c r="E26" t="n">
-        <v>1.312</v>
+        <v>1.5</v>
       </c>
       <c r="F26" t="n">
         <v>1.31</v>
@@ -2013,7 +2108,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1082 Overall Length = 3.500 (table had 3.44); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1082 Side 1 ID = 1.312 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1082 Overall Length = 3.500 (table had 3.44); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1082 Side 1 ID = 1.312 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.44 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 1.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.312) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.5 -&gt; Air-Way 3.44 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 1.312 -&gt; Air-Way 1.5</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2034,7 +2134,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="C27" t="n">
         <v>1.81</v>
@@ -2043,7 +2143,7 @@
         <v>2.13</v>
       </c>
       <c r="E27" t="n">
-        <v>1.312</v>
+        <v>1.5</v>
       </c>
       <c r="F27" t="n">
         <v>1.31</v>
@@ -2076,12 +2176,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1097 Overall Length = 3.500 (table had 3.44); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1097 Side 1 ID = 1.312 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; THDMAJ_A@DRIVE: 1.900 = ASME B1.20.1 1-1/2 NPT OD (ms51500.NPTF[24]) for the part-number dash -24 (table had empty: Air-Way callout "1 1/2-11" = nominal 1 1/2 with a TPI misprint); OMi Items!U1097 "1 1/2-11 1/2 NPFT" and Brennan TFA p9 "1-1/2-11-1/2" agree [thread size from the OMi dimension file's own thread cell Items!U1097 (OMi first, user 2026-09-25), not a dash transfer; Q18 / Q-THREAD not needed (impact F45D) - single source, ASSUMED] [batch 15 2026-10-02, staged]</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1097 Overall Length = 3.500 (table had 3.44); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1097 Side 1 ID = 1.312 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; THDMAJ_A@DRIVE: 1.900 = ASME B1.20.1 1-1/2 NPT OD (ms51500.NPTF[24]) for the part-number dash -24 (table had empty: Air-Way callout "1 1/2-11" = nominal 1 1/2 with a TPI misprint); OMi Items!U1097 "1 1/2-11 1/2 NPFT" and Brennan TFA p9 "1-1/2-11-1/2" agree [thread size from the OMi dimension file's own thread cell Items!U1097 (OMi first, user 2026-09-25), not a dash transfer; Q18 / Q-THREAD not needed (impact F45D) - single source, ASSUMED] [batch 15 2026-10-02, staged]; L25@DRIVE: Air-Way 3.44 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 1.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.312) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>A NPTF printed "1 1/2-11" on Air-Way (sibling 1 1/2-11 1/2); copied as printed in $PRP@Threads - as-printed, likely typo | RESOLVED 2026-10-02 (batch 15, staged): THDMAJ_A = 1.900, the 1-1/2 NPT of the part-number dash -24 (ASME B1.20.1); OMi Items!U1097 prints "1 1/2-11 1/2 NPFT" and Brennan TFA p9 2706-24-24 prints "1-1/2-11-1/2"; the OMi thread cell is the source (no dash transfer, Q-THREAD not needed per impact F45D) - ASSUMED</t>
+          <t>A NPTF printed "1 1/2-11" on Air-Way (sibling 1 1/2-11 1/2); copied as printed in $PRP@Threads - as-printed, likely typo | RESOLVED 2026-10-02 (batch 15, staged): THDMAJ_A = 1.900, the 1-1/2 NPT of the part-number dash -24 (ASME B1.20.1); OMi Items!U1097 prints "1 1/2-11 1/2 NPFT" and Brennan TFA p9 2706-24-24 prints "1-1/2-11-1/2"; the OMi thread cell is the source (no dash transfer, Q-THREAD not needed per impact F45D) - ASSUMED | 2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.5 -&gt; Air-Way 3.44 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 1.312 -&gt; Air-Way 1.5</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_2706.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2706.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2274,24 +2274,55 @@
           <t>2706-06-04</t>
         </is>
       </c>
+      <c r="B29" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>2706-06-04</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>3/8-18 (A NPTF) x 7/16-20 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L25 / hex / D1 / D = OMi WebsitePartsInfo2026.xlsx Items row 1073; I1 1.20 = Air-Way -04 bulkhead (A8); thread majors from the end library; not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 1073 + A8 I1 per size; not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2302,6 +2333,11 @@
       <c r="P29" t="inlineStr">
         <is>
           <t>2706-06-04</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
@@ -2311,24 +2347,55 @@
           <t>2706-32-32</t>
         </is>
       </c>
+      <c r="B30" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>2706-32-32</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2-11 1/2 (A NPTF) x 2 1/2-12 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L25 / hex / D1 / D = OMi WebsitePartsInfo2026.xlsx Items row 1083; I1 2.09 = Air-Way -32 bulkhead (A8); thread majors from the end library; cross-check Brennan TFA p9 2706-32-32: L 3.91, C1 HEX 2.750, A1 DRILL 1.938, B2 DRILL 1.781 - all equal (same manufacturer, one source)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 1083 + A8 I1 per size; cross-check Brennan TFA p9 2706-32-32: L 3.91, C1 HEX 2.750, A1 DRILL 1.938, B2 DRILL 1.781 - all equal (same manufacturer, one source)</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2339,6 +2406,11 @@
       <c r="P30" t="inlineStr">
         <is>
           <t>2706-32-32</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
@@ -2421,24 +2493,55 @@
           <t>2706-LN-06-04</t>
         </is>
       </c>
+      <c r="B32" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>2706-LN-06-04</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>3/8-18 (A NPTF) x 7/16-20 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L25 / hex / D1 / D = OMi WebsitePartsInfo2026.xlsx Items row 1088; I1 1.20 = Air-Way -04 bulkhead (A8); -LN modelled as the plain part, no locknut (A10); thread majors from the end library; own -LN row = the plain 2706-06-04 (Items row 1073); not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 1088 + A8 I1 per size + A10; own -LN row = the plain 2706-06-04 (Items row 1073); not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2449,6 +2552,11 @@
       <c r="P32" t="inlineStr">
         <is>
           <t>2706-LN-06-04</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
@@ -2458,24 +2566,55 @@
           <t>2706-LN-08-06</t>
         </is>
       </c>
+      <c r="B33" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>2706-LN-08-06</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>1/2-14 (A NPTF) x 9/16-18 (B UN/UNF-2A)</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): every size = the plain twin 2706-08-06 = Air-Way 2706.csv line 12 (2706-8-6, the plain twin; = the live review row 2706-08-06) (A10: -LN modelled as the plain part, no locknut; Air-Way first 2026-10-20); OMi own -LN row (Items row 1091) L 2.400 / hex 0.875 / D1 0.531 / D 0.295 and Brennan TFA p9 2706-08-06 L 2.410 / B2 DRILL 0.297 not used (Air-Way prints the part)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): = the plain 2706-08-06 (A10); OMi -LN row L 2.400 / D 0.295 and Brennan L 2.410 differ from Air-Way (2.34 / 0.30) - Air-Way first (2026-10-20), as on the plain twin</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
